--- a/materials/Excel_Exercises_in_class_session_1_solutions.xlsx
+++ b/materials/Excel_Exercises_in_class_session_1_solutions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Introduction to Programming\Exercises_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C79BB90-EF38-4EBA-88AE-94C99C5FE8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644829AB-3490-469F-9209-8C9FC628A19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25035" windowHeight="14310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21885" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Future_Value" sheetId="9" r:id="rId1"/>
@@ -45,24 +45,11 @@
     <definedName name="solver_ucut" hidden="1">1E+30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="147">
   <si>
     <t>DAX</t>
   </si>
@@ -499,7 +486,10 @@
     <t>"=VLOOKUP($F$13,$A$2:$G$11,6,FALSE)*0.3"</t>
   </si>
   <si>
-    <t>"=(VLOOKUP($F$13,$A$2:$G$11,3,FALSE)+VLOOKUP($F$13,$A$2:$G$11,5,FALSE)+VLOOKUP($F$13,$A$2:$G$11,7,FALSE))/3*0.1"</t>
+    <t>TODO: update the formula in F17 (should be identical to H17)</t>
+  </si>
+  <si>
+    <t>"=AVERAGE(VLOOKUP($F$13,$A$2:$G$11,3,FALSE)+VLOOKUP($F$13,$A$2:$G$11,5,FALSE)+VLOOKUP($F$13,$A$2:$G$11,7,FALSE))/15*10"</t>
   </si>
 </sst>
 </file>
@@ -507,8 +497,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -774,7 +764,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -858,12 +848,12 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
@@ -6549,7 +6539,7 @@
       </c>
       <c r="G17" s="20"/>
       <c r="H17" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -6559,6 +6549,11 @@
       <c r="F18" s="27">
         <f>SUM(F14:F17)</f>
         <v>65.86666666666666</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F20" s="16" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="11:11" x14ac:dyDescent="0.2">
